--- a/stories/arbres/TREE-SEC-004.xlsx
+++ b/stories/arbres/TREE-SEC-004.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Noé est avec Maman. Ils sont au bord de la mer. C'est la petite maison. Noé a des jouets. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. On appelle Maman. Papa est sur la terrasse.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>12</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1538,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Noé prend le ballon rouge. C'est un jouet. Les mains restent avec les jouets. Noé appelle un adulte. Il appelle Maman. Maman dit : je suis là.</t>
+          <t>Noé prend le ballon rouge. C'est un jouet. Les mains restent avec les jouets. Noé appelle un adulte. Il appelle Maman. Je suis là.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1653,6 +1680,12 @@
         <v>12</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Noé prend le ballon rouge. C'est un jouet. Les mains restent avec les jouets. Noé appelle un adulte. Il appelle Maman.
+maman|Je suis là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1837,6 +1870,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Les mains sont où ? Avec les jouets.</t>
         </is>
       </c>
     </row>
@@ -2009,6 +2047,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Noé retient : appeler un adulte, mains avec les jouets. Les mains restent avec les jouets. On continue, avec Maman.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2197,6 +2240,11 @@
       <c r="AV7" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -2365,6 +2413,11 @@
         <v>12</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a choisi Tom. On entend la mer. Noé joue avec Tom. Les mains restent avec les jouets. On appelle un adulte. On appelle Maman. Les mains restent avec les jouets. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2551,6 +2604,11 @@
         <v>12</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2717,6 +2775,11 @@
         <v>12</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. Le seau cliquette. C'est le matin. La lumière est claire. Noé appelle Maman. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Noé dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2879,6 +2942,11 @@
         <v>12</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3045,6 +3113,11 @@
         <v>12</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|C'est après la sieste. Un oiseau chante. C'est après la sieste. Noé a les jouets. Il appelle un adulte. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Noé dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3207,6 +3280,11 @@
         <v>12</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3373,6 +3451,11 @@
         <v>12</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. Le sable est chaud. C'est le soir. Noé range. Les mains restent avec les jouets. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Noé dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3535,6 +3618,11 @@
         <v>12</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3701,6 +3789,11 @@
         <v>12</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a choisi Léa. Le vent est doux. Noé joue avec Léa. Les mains restent avec les jouets. On appelle un adulte. On appelle Maman. Les mains restent avec les jouets. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3887,6 +3980,11 @@
         <v>12</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4053,6 +4151,11 @@
         <v>12</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. Un oiseau chante. C'est le matin. La lumière est claire. Noé appelle Maman. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Noé dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4215,6 +4318,11 @@
         <v>12</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4381,6 +4489,11 @@
         <v>12</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|C'est après la sieste. Le sable est chaud. C'est après la sieste. Noé a les jouets. Il appelle un adulte. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Noé dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4543,6 +4656,11 @@
         <v>12</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4709,6 +4827,11 @@
         <v>12</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. L'eau chuchote. C'est le soir. Noé range. Les mains restent avec les jouets. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Noé dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4871,6 +4994,11 @@
         <v>12</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5037,6 +5165,11 @@
         <v>12</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a choisi Sami. Le seau cliquette. Noé joue avec Sami. Les mains restent avec les jouets. On appelle un adulte. On appelle Maman. Les mains restent avec les jouets. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5223,6 +5356,11 @@
         <v>12</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5389,6 +5527,11 @@
         <v>12</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. Le sable est chaud. C'est le matin. La lumière est claire. Noé appelle Maman. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Noé dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5551,6 +5694,11 @@
         <v>12</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5717,6 +5865,11 @@
         <v>12</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|C'est après la sieste. L'eau chuchote. C'est après la sieste. Noé a les jouets. Il appelle un adulte. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Noé dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5879,6 +6032,11 @@
         <v>12</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6045,6 +6203,11 @@
         <v>12</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. On entend la mer. C'est le soir. Noé range. Les mains restent avec les jouets. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Noé dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6207,6 +6370,11 @@
         <v>12</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6373,6 +6541,11 @@
         <v>12</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Noé prend le seau bleu. C'est un jouet. Les mains restent avec les jouets. Noé appelle un adulte. Il appelle Maman. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6557,6 +6730,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Les mains sont où ? Avec les jouets.</t>
         </is>
       </c>
     </row>
@@ -6729,6 +6907,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Noé retient : appeler un adulte, mains avec les jouets. Les mains restent avec les jouets. On continue, avec Maman.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6917,6 +7100,11 @@
       <c r="AV35" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -7085,6 +7273,11 @@
         <v>12</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a choisi Tom. Un oiseau chante. Noé joue avec Tom. Les mains restent avec les jouets. On appelle un adulte. On appelle Maman. Les mains restent avec les jouets. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7271,6 +7464,11 @@
         <v>12</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7437,6 +7635,11 @@
         <v>12</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. Un oiseau chante. C'est le matin. La lumière est claire. Noé appelle Maman. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Noé dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7599,6 +7802,11 @@
         <v>12</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7765,6 +7973,11 @@
         <v>12</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|C'est après la sieste. Le sable est chaud. C'est après la sieste. Noé a les jouets. Il appelle un adulte. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Noé dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7927,6 +8140,11 @@
         <v>12</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8093,6 +8311,11 @@
         <v>12</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. L'eau chuchote. C'est le soir. Noé range. Les mains restent avec les jouets. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Noé dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8255,6 +8478,11 @@
         <v>12</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8421,6 +8649,11 @@
         <v>12</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a choisi Léa. Le sable est chaud. Noé joue avec Léa. Les mains restent avec les jouets. On appelle un adulte. On appelle Maman. Les mains restent avec les jouets. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8607,6 +8840,11 @@
         <v>12</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8773,6 +9011,11 @@
         <v>12</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. Le sable est chaud. C'est le matin. La lumière est claire. Noé appelle Maman. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Noé dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8935,6 +9178,11 @@
         <v>12</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9101,6 +9349,11 @@
         <v>12</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|C'est après la sieste. L'eau chuchote. C'est après la sieste. Noé a les jouets. Il appelle un adulte. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Noé dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9263,6 +9516,11 @@
         <v>12</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9429,6 +9687,11 @@
         <v>12</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. On entend la mer. C'est le soir. Noé range. Les mains restent avec les jouets. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Noé dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9591,6 +9854,11 @@
         <v>12</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9757,6 +10025,11 @@
         <v>12</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a choisi Sami. L'eau chuchote. Noé joue avec Sami. Les mains restent avec les jouets. On appelle un adulte. On appelle Maman. Les mains restent avec les jouets. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9943,6 +10216,11 @@
         <v>12</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10109,6 +10387,11 @@
         <v>12</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. L'eau chuchote. C'est le matin. La lumière est claire. Noé appelle Maman. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Noé dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10271,6 +10554,11 @@
         <v>12</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10437,6 +10725,11 @@
         <v>12</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|C'est après la sieste. On entend la mer. C'est après la sieste. Noé a les jouets. Il appelle un adulte. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Noé dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10599,6 +10892,11 @@
         <v>12</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10765,6 +11063,11 @@
         <v>12</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. Le vent est doux. C'est le soir. Noé range. Les mains restent avec les jouets. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Noé dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10927,6 +11230,11 @@
         <v>12</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11093,6 +11401,11 @@
         <v>12</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Noé prend le doudou. C'est un jouet. Les mains restent avec les jouets. Noé appelle un adulte. Il appelle Maman. Papa écoute aussi.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11277,6 +11590,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Les mains sont où ? Avec les jouets.</t>
         </is>
       </c>
     </row>
@@ -11449,6 +11767,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Noé retient : appeler un adulte, mains avec les jouets. Les mains restent avec les jouets. On continue, avec Maman.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11637,6 +11960,11 @@
       <c r="AV63" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -11805,6 +12133,11 @@
         <v>12</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a choisi Tom. On entend la mer. Noé joue avec Tom. Les mains restent avec les jouets. On appelle un adulte. On appelle Maman. Les mains restent avec les jouets. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11991,6 +12324,11 @@
         <v>12</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12157,6 +12495,11 @@
         <v>12</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. Le sable est chaud. C'est le matin. La lumière est claire. Noé appelle Maman. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Noé dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12319,6 +12662,11 @@
         <v>12</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12485,6 +12833,11 @@
         <v>12</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|C'est après la sieste. L'eau chuchote. C'est après la sieste. Noé a les jouets. Il appelle un adulte. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Noé dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12647,6 +13000,11 @@
         <v>12</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12813,6 +13171,11 @@
         <v>12</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. On entend la mer. C'est le soir. Noé range. Les mains restent avec les jouets. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Noé dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12975,6 +13338,11 @@
         <v>12</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13141,6 +13509,11 @@
         <v>12</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a choisi Léa. Le vent est doux. Noé joue avec Léa. Les mains restent avec les jouets. On appelle un adulte. On appelle Maman. Les mains restent avec les jouets. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13327,6 +13700,11 @@
         <v>12</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13493,6 +13871,11 @@
         <v>12</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. L'eau chuchote. C'est le matin. La lumière est claire. Noé appelle Maman. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Noé dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13655,6 +14038,11 @@
         <v>12</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13821,6 +14209,11 @@
         <v>12</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|C'est après la sieste. On entend la mer. C'est après la sieste. Noé a les jouets. Il appelle un adulte. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Noé dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13983,6 +14376,11 @@
         <v>12</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14149,6 +14547,11 @@
         <v>12</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. Le vent est doux. C'est le soir. Noé range. Les mains restent avec les jouets. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Noé dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14311,6 +14714,11 @@
         <v>12</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14477,6 +14885,11 @@
         <v>12</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a choisi Sami. Le seau cliquette. Noé joue avec Sami. Les mains restent avec les jouets. On appelle un adulte. On appelle Maman. Les mains restent avec les jouets. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14663,6 +15076,11 @@
         <v>12</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14829,6 +15247,11 @@
         <v>12</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. On entend la mer. C'est le matin. La lumière est claire. Noé appelle Maman. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Noé dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14991,6 +15414,11 @@
         <v>12</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15157,6 +15585,11 @@
         <v>12</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|C'est après la sieste. Le vent est doux. C'est après la sieste. Noé a les jouets. Il appelle un adulte. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Noé dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15319,6 +15752,11 @@
         <v>12</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15485,6 +15923,11 @@
         <v>12</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. Le seau cliquette. C'est le soir. Noé range. Les mains restent avec les jouets. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Noé dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15647,6 +16090,11 @@
         <v>12</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15665,7 +16113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15696,6 +16144,13 @@
       <c r="A4" t="inlineStr">
         <is>
           <t>ch2C: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-SEC-004.xlsx
+++ b/stories/arbres/TREE-SEC-004.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Aujourd'hui, Noé est avec Maman. Ils sont au bord de la mer. C'est la petite maison. Noé a des jouets. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. On appelle Maman. Papa est sur la terrasse.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1686,6 +1693,7 @@
 maman|Je suis là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1877,6 +1885,7 @@
           <t>narrateur|Les mains sont où ? Avec les jouets.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2052,6 +2061,7 @@
           <t>narrateur|Oui. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Noé retient : appeler un adulte, mains avec les jouets. Les mains restent avec les jouets. On continue, avec Maman.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2247,6 +2257,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2418,6 +2429,7 @@
           <t>narrateur|Noé a choisi Tom. On entend la mer. Noé joue avec Tom. Les mains restent avec les jouets. On appelle un adulte. On appelle Maman. Les mains restent avec les jouets. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2609,6 +2621,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2780,6 +2793,7 @@
           <t>narrateur|C'est le matin. Le seau cliquette. C'est le matin. La lumière est claire. Noé appelle Maman. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Noé dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2947,6 +2961,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3118,6 +3133,7 @@
           <t>narrateur|C'est après la sieste. Un oiseau chante. C'est après la sieste. Noé a les jouets. Il appelle un adulte. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Noé dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3285,6 +3301,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3456,6 +3473,7 @@
           <t>narrateur|C'est le soir. Le sable est chaud. C'est le soir. Noé range. Les mains restent avec les jouets. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Noé dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3623,6 +3641,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3794,6 +3813,7 @@
           <t>narrateur|Noé a choisi Léa. Le vent est doux. Noé joue avec Léa. Les mains restent avec les jouets. On appelle un adulte. On appelle Maman. Les mains restent avec les jouets. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3985,6 +4005,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4156,6 +4177,7 @@
           <t>narrateur|C'est le matin. Un oiseau chante. C'est le matin. La lumière est claire. Noé appelle Maman. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Noé dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4323,6 +4345,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4494,6 +4517,7 @@
           <t>narrateur|C'est après la sieste. Le sable est chaud. C'est après la sieste. Noé a les jouets. Il appelle un adulte. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Noé dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4661,6 +4685,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4832,6 +4857,7 @@
           <t>narrateur|C'est le soir. L'eau chuchote. C'est le soir. Noé range. Les mains restent avec les jouets. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Noé dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4999,6 +5025,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5170,6 +5197,7 @@
           <t>narrateur|Noé a choisi Sami. Le seau cliquette. Noé joue avec Sami. Les mains restent avec les jouets. On appelle un adulte. On appelle Maman. Les mains restent avec les jouets. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5361,6 +5389,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5532,6 +5561,7 @@
           <t>narrateur|C'est le matin. Le sable est chaud. C'est le matin. La lumière est claire. Noé appelle Maman. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Noé dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5699,6 +5729,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5870,6 +5901,7 @@
           <t>narrateur|C'est après la sieste. L'eau chuchote. C'est après la sieste. Noé a les jouets. Il appelle un adulte. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Noé dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -6037,6 +6069,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6208,6 +6241,7 @@
           <t>narrateur|C'est le soir. On entend la mer. C'est le soir. Noé range. Les mains restent avec les jouets. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Noé dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6375,6 +6409,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6546,6 +6581,7 @@
           <t>narrateur|Noé prend le seau bleu. C'est un jouet. Les mains restent avec les jouets. Noé appelle un adulte. Il appelle Maman. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6737,6 +6773,7 @@
           <t>narrateur|Les mains sont où ? Avec les jouets.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6912,6 +6949,7 @@
           <t>narrateur|Oui. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Noé retient : appeler un adulte, mains avec les jouets. Les mains restent avec les jouets. On continue, avec Maman.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7107,6 +7145,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7278,6 +7317,7 @@
           <t>narrateur|Noé a choisi Tom. Un oiseau chante. Noé joue avec Tom. Les mains restent avec les jouets. On appelle un adulte. On appelle Maman. Les mains restent avec les jouets. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7469,6 +7509,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7640,6 +7681,7 @@
           <t>narrateur|C'est le matin. Un oiseau chante. C'est le matin. La lumière est claire. Noé appelle Maman. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Noé dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7807,6 +7849,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7978,6 +8021,7 @@
           <t>narrateur|C'est après la sieste. Le sable est chaud. C'est après la sieste. Noé a les jouets. Il appelle un adulte. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Noé dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8145,6 +8189,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8316,6 +8361,7 @@
           <t>narrateur|C'est le soir. L'eau chuchote. C'est le soir. Noé range. Les mains restent avec les jouets. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Noé dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8483,6 +8529,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8654,6 +8701,7 @@
           <t>narrateur|Noé a choisi Léa. Le sable est chaud. Noé joue avec Léa. Les mains restent avec les jouets. On appelle un adulte. On appelle Maman. Les mains restent avec les jouets. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8845,6 +8893,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -9016,6 +9065,7 @@
           <t>narrateur|C'est le matin. Le sable est chaud. C'est le matin. La lumière est claire. Noé appelle Maman. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Noé dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9183,6 +9233,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9354,6 +9405,7 @@
           <t>narrateur|C'est après la sieste. L'eau chuchote. C'est après la sieste. Noé a les jouets. Il appelle un adulte. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Noé dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9521,6 +9573,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9692,6 +9745,7 @@
           <t>narrateur|C'est le soir. On entend la mer. C'est le soir. Noé range. Les mains restent avec les jouets. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Noé dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9859,6 +9913,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -10030,6 +10085,7 @@
           <t>narrateur|Noé a choisi Sami. L'eau chuchote. Noé joue avec Sami. Les mains restent avec les jouets. On appelle un adulte. On appelle Maman. Les mains restent avec les jouets. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10221,6 +10277,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10392,6 +10449,7 @@
           <t>narrateur|C'est le matin. L'eau chuchote. C'est le matin. La lumière est claire. Noé appelle Maman. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Noé dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10559,6 +10617,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10730,6 +10789,7 @@
           <t>narrateur|C'est après la sieste. On entend la mer. C'est après la sieste. Noé a les jouets. Il appelle un adulte. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Noé dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10897,6 +10957,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -11068,6 +11129,7 @@
           <t>narrateur|C'est le soir. Le vent est doux. C'est le soir. Noé range. Les mains restent avec les jouets. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Noé dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11235,6 +11297,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11406,6 +11469,7 @@
           <t>narrateur|Noé prend le doudou. C'est un jouet. Les mains restent avec les jouets. Noé appelle un adulte. Il appelle Maman. Papa écoute aussi.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11597,6 +11661,7 @@
           <t>narrateur|Les mains sont où ? Avec les jouets.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11772,6 +11837,7 @@
           <t>narrateur|Oui. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Noé retient : appeler un adulte, mains avec les jouets. Les mains restent avec les jouets. On continue, avec Maman.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11967,6 +12033,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12138,6 +12205,7 @@
           <t>narrateur|Noé a choisi Tom. On entend la mer. Noé joue avec Tom. Les mains restent avec les jouets. On appelle un adulte. On appelle Maman. Les mains restent avec les jouets. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12329,6 +12397,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12500,6 +12569,7 @@
           <t>narrateur|C'est le matin. Le sable est chaud. C'est le matin. La lumière est claire. Noé appelle Maman. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Noé dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12667,6 +12737,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12838,6 +12909,7 @@
           <t>narrateur|C'est après la sieste. L'eau chuchote. C'est après la sieste. Noé a les jouets. Il appelle un adulte. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Noé dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -13005,6 +13077,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13176,6 +13249,7 @@
           <t>narrateur|C'est le soir. On entend la mer. C'est le soir. Noé range. Les mains restent avec les jouets. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Noé dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13343,6 +13417,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13514,6 +13589,7 @@
           <t>narrateur|Noé a choisi Léa. Le vent est doux. Noé joue avec Léa. Les mains restent avec les jouets. On appelle un adulte. On appelle Maman. Les mains restent avec les jouets. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13705,6 +13781,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13876,6 +13953,7 @@
           <t>narrateur|C'est le matin. L'eau chuchote. C'est le matin. La lumière est claire. Noé appelle Maman. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Noé dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -14043,6 +14121,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14214,6 +14293,7 @@
           <t>narrateur|C'est après la sieste. On entend la mer. C'est après la sieste. Noé a les jouets. Il appelle un adulte. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Noé dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14381,6 +14461,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14552,6 +14633,7 @@
           <t>narrateur|C'est le soir. Le vent est doux. C'est le soir. Noé range. Les mains restent avec les jouets. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Noé dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14719,6 +14801,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14890,6 +14973,7 @@
           <t>narrateur|Noé a choisi Sami. Le seau cliquette. Noé joue avec Sami. Les mains restent avec les jouets. On appelle un adulte. On appelle Maman. Les mains restent avec les jouets. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -15081,6 +15165,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15252,6 +15337,7 @@
           <t>narrateur|C'est le matin. On entend la mer. C'est le matin. La lumière est claire. Noé appelle Maman. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Noé dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15419,6 +15505,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15590,6 +15677,7 @@
           <t>narrateur|C'est après la sieste. Le vent est doux. C'est après la sieste. Noé a les jouets. Il appelle un adulte. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Noé dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15757,6 +15845,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15928,6 +16017,7 @@
           <t>narrateur|C'est le soir. Le seau cliquette. C'est le soir. Noé range. Les mains restent avec les jouets. Les mains restent avec les jouets. Pour la lumière, on appelle un adulte. Noé dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -16095,6 +16185,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -16113,7 +16204,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16151,6 +16242,20 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16165,7 +16270,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16352,6 +16457,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
